--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>R$ 636.485,11</t>
-  </si>
-  <si>
-    <t>R$ 3.297,85
-R$ 3.358,88</t>
+183</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>R$ 639.918,24</t>
+  </si>
+  <si>
+    <t>R$ 3.298,55
+R$ 3.359,29</t>
   </si>
   <si>
     <t>5.7%
-7.7%</t>
+7.6%</t>
   </si>
   <si>
     <t>36.8</t>
   </si>
   <si>
-    <t>(2.3%)</t>
-  </si>
-  <si>
-    <t>(373.1%)</t>
-  </si>
-  <si>
-    <t>(415.3%)</t>
+    <t>(2.4%)</t>
+  </si>
+  <si>
+    <t>(370.9%)</t>
+  </si>
+  <si>
+    <t>(413.1%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,10 +950,10 @@
     <t>26.5</t>
   </si>
   <si>
-    <t>73.4%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
+    <t>73.3%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -8790,7 +8790,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8826,27 +8826,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.010029302391263428</v>
+      </c>
+      <c r="R58" s="7">
+        <v>39</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.15217391304347827</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.31234989645017813</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.038592246725291497</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.015494898241546344</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0094065765059872467</v>
+      </c>
+      <c r="X58" s="8">
+        <v>25.015054838709677</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>5.0223684210526311</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>5.3394433333333335</v>
+      </c>
       <c r="AC58" s="8">
         <v>10.530303999999999</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>17.240861290322577</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.77419354838709675</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -17051,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17444,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18621,7 +18655,7 @@
         <v>-14.9</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20939,7 +20973,7 @@
         <v>-740.86000000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22223,7 +22257,7 @@
         <v>-73.799999999999997</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24301,7 +24335,9 @@
       <c r="AB179" s="8">
         <v>1.4992409090909091</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.7689380000000003</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.715909090909092</v>
       </c>
@@ -28386,7 +28422,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
